--- a/mlb_weather_professional_v5_2026_08_01.xlsx
+++ b/mlb_weather_professional_v5_2026_08_01.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="420">
   <si>
     <t>Date</t>
   </si>
@@ -617,7 +617,16 @@
     <t>🔴 Poor</t>
   </si>
   <si>
-    <t>FIRST RUN</t>
+    <t>IMPROVING</t>
+  </si>
+  <si>
+    <t>IMPROVING RAPIDLY</t>
+  </si>
+  <si>
+    <t>WORSENING RAPIDLY</t>
+  </si>
+  <si>
+    <t>STEADY</t>
   </si>
   <si>
     <t>LOW</t>
@@ -635,49 +644,49 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-07-31 10:58:54 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-31 10:58:56 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-31 10:58:57 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-31 10:58:58 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-31 10:58:59 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-31 10:59:01 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-31 10:59:02 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-31 10:59:03 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-31 10:59:05 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-31 10:59:06 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-31 10:59:08 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-31 10:59:09 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-31 10:59:10 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-31 10:59:11 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-31 10:59:13 PM PDT</t>
+    <t>2026-07-31 10:59:29 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-31 10:59:30 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-31 10:59:32 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-31 10:59:33 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-31 10:59:34 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-31 10:59:35 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-31 10:59:36 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-31 10:59:37 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-31 10:59:38 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-31 10:59:40 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-31 10:59:41 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-31 10:59:42 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-31 10:59:43 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-31 10:59:45 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-31 10:59:46 PM PDT</t>
   </si>
   <si>
     <t>Period</t>
@@ -1085,49 +1094,49 @@
     <t>09:40 PM PDT</t>
   </si>
   <si>
-    <t>2026-08-01 05:58:54 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-01 05:58:56 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-01 05:58:57 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-01 05:58:58 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-01 05:58:59 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-01 05:59:01 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-01 05:59:02 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-01 05:59:03 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-01 05:59:05 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-01 05:59:06 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-01 05:59:08 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-01 05:59:09 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-01 05:59:10 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-01 05:59:11 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-01 05:59:13 UTC</t>
+    <t>2026-08-01 05:59:29 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-01 05:59:30 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-01 05:59:32 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-01 05:59:33 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-01 05:59:34 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-01 05:59:35 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-01 05:59:36 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-01 05:59:37 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-01 05:59:38 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-01 05:59:40 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-01 05:59:41 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-01 05:59:42 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-01 05:59:43 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-01 05:59:45 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-01 05:59:46 UTC</t>
   </si>
   <si>
     <t>2026-07-31T18:26:38+00:00</t>
@@ -1757,7 +1766,7 @@
     <col min="40" max="40" width="22.7109375" customWidth="1"/>
     <col min="41" max="41" width="17.7109375" customWidth="1"/>
     <col min="42" max="42" width="15.7109375" customWidth="1"/>
-    <col min="43" max="43" width="16.7109375" customWidth="1"/>
+    <col min="43" max="43" width="19.7109375" customWidth="1"/>
     <col min="44" max="44" width="34.7109375" customWidth="1"/>
     <col min="45" max="45" width="33.7109375" customWidth="1"/>
     <col min="46" max="46" width="32.7109375" customWidth="1"/>
@@ -2057,7 +2066,7 @@
         <v>198</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS2">
         <v>0</v>
@@ -2066,19 +2075,19 @@
         <v>8</v>
       </c>
       <c r="AU2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AV2">
         <v>2.9</v>
       </c>
       <c r="AW2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AX2">
         <v>1.3</v>
       </c>
       <c r="AY2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AZ2">
         <v>0</v>
@@ -2212,10 +2221,10 @@
         <v>60.2</v>
       </c>
       <c r="AQ3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3">
         <v>0</v>
@@ -2224,22 +2233,22 @@
         <v>7</v>
       </c>
       <c r="AU3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AV3">
         <v>18.3</v>
       </c>
       <c r="AW3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AX3">
         <v>11</v>
       </c>
       <c r="AY3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AZ3">
-        <v>692.3</v>
+        <v>692.9</v>
       </c>
       <c r="BA3">
         <v>5</v>
@@ -2373,7 +2382,7 @@
         <v>198</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS4">
         <v>-0.05</v>
@@ -2382,22 +2391,22 @@
         <v>10</v>
       </c>
       <c r="AU4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AV4">
         <v>0</v>
       </c>
       <c r="AW4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AX4">
         <v>17.7</v>
       </c>
       <c r="AY4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AZ4">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="BA4">
         <v>5</v>
@@ -2528,10 +2537,10 @@
         <v>55.8</v>
       </c>
       <c r="AQ5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AS5">
         <v>-0.21</v>
@@ -2540,22 +2549,22 @@
         <v>10</v>
       </c>
       <c r="AU5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AV5">
         <v>3.6</v>
       </c>
       <c r="AW5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AX5">
         <v>25.7</v>
       </c>
       <c r="AY5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AZ5">
-        <v>219.8</v>
+        <v>220.4</v>
       </c>
       <c r="BA5">
         <v>5</v>
@@ -2686,10 +2695,10 @@
         <v>90.59999999999999</v>
       </c>
       <c r="AQ6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AS6">
         <v>0</v>
@@ -2698,22 +2707,22 @@
         <v>8</v>
       </c>
       <c r="AU6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AV6">
         <v>63.3</v>
       </c>
       <c r="AW6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AX6">
         <v>14.6</v>
       </c>
       <c r="AY6" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AZ6">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="BA6">
         <v>5</v>
@@ -2844,10 +2853,10 @@
         <v>57</v>
       </c>
       <c r="AQ7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AS7">
         <v>0</v>
@@ -2856,22 +2865,22 @@
         <v>7</v>
       </c>
       <c r="AU7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AV7">
         <v>4.1</v>
       </c>
       <c r="AW7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AX7">
         <v>9.699999999999999</v>
       </c>
       <c r="AY7" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AZ7">
-        <v>185.8</v>
+        <v>186.4</v>
       </c>
       <c r="BA7">
         <v>5</v>
@@ -3005,7 +3014,7 @@
         <v>198</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AS8">
         <v>0</v>
@@ -3014,22 +3023,22 @@
         <v>7</v>
       </c>
       <c r="AU8" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AV8">
         <v>0</v>
       </c>
       <c r="AW8" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AX8">
         <v>28</v>
       </c>
       <c r="AY8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AZ8">
-        <v>17.9</v>
+        <v>18.5</v>
       </c>
       <c r="BA8">
         <v>5</v>
@@ -3160,10 +3169,10 @@
         <v>63.9</v>
       </c>
       <c r="AQ9" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="AS9">
         <v>0</v>
@@ -3172,22 +3181,22 @@
         <v>8</v>
       </c>
       <c r="AU9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AV9">
         <v>27.6</v>
       </c>
       <c r="AW9" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AX9">
         <v>19</v>
       </c>
       <c r="AY9" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AZ9">
-        <v>597.2</v>
+        <v>597.8</v>
       </c>
       <c r="BA9">
         <v>5</v>
@@ -3318,10 +3327,10 @@
         <v>88.3</v>
       </c>
       <c r="AQ10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AS10">
         <v>0</v>
@@ -3330,22 +3339,22 @@
         <v>9</v>
       </c>
       <c r="AU10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AV10">
         <v>57.1</v>
       </c>
       <c r="AW10" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AX10">
         <v>23.2</v>
       </c>
       <c r="AY10" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AZ10">
-        <v>71.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="BA10">
         <v>5</v>
@@ -3476,10 +3485,10 @@
         <v>89.7</v>
       </c>
       <c r="AQ11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>-10.3</v>
       </c>
       <c r="AS11">
         <v>0</v>
@@ -3488,22 +3497,22 @@
         <v>7</v>
       </c>
       <c r="AU11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AV11">
         <v>47</v>
       </c>
       <c r="AW11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AX11">
         <v>16.7</v>
       </c>
       <c r="AY11" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AZ11">
-        <v>257.6</v>
+        <v>258.2</v>
       </c>
       <c r="BA11">
         <v>5</v>
@@ -3634,10 +3643,10 @@
         <v>17.7</v>
       </c>
       <c r="AQ12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS12">
         <v>0</v>
@@ -3646,22 +3655,22 @@
         <v>7</v>
       </c>
       <c r="AU12" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AV12">
         <v>1.4</v>
       </c>
       <c r="AW12" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AX12">
         <v>17.7</v>
       </c>
       <c r="AY12" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AZ12">
-        <v>207.5</v>
+        <v>208.1</v>
       </c>
       <c r="BA12">
         <v>5</v>
@@ -3792,10 +3801,10 @@
         <v>74.5</v>
       </c>
       <c r="AQ13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="AS13">
         <v>0</v>
@@ -3804,22 +3813,22 @@
         <v>7</v>
       </c>
       <c r="AU13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AV13">
         <v>0</v>
       </c>
       <c r="AW13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AX13">
         <v>10.6</v>
       </c>
       <c r="AY13" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AZ13">
-        <v>112.4</v>
+        <v>113</v>
       </c>
       <c r="BA13">
         <v>5</v>
@@ -3953,7 +3962,7 @@
         <v>198</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AS14">
         <v>0</v>
@@ -3962,22 +3971,22 @@
         <v>7</v>
       </c>
       <c r="AU14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AV14">
         <v>0.1</v>
       </c>
       <c r="AW14" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AX14">
         <v>21.1</v>
       </c>
       <c r="AY14" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AZ14">
-        <v>112.3</v>
+        <v>112.8</v>
       </c>
       <c r="BA14">
         <v>5</v>
@@ -4111,7 +4120,7 @@
         <v>198</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AS15">
         <v>-0.62</v>
@@ -4120,22 +4129,22 @@
         <v>10</v>
       </c>
       <c r="AU15" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AV15">
         <v>0.2</v>
       </c>
       <c r="AW15" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AX15">
         <v>11.1</v>
       </c>
       <c r="AY15" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AZ15">
-        <v>112.4</v>
+        <v>113</v>
       </c>
       <c r="BA15">
         <v>5</v>
@@ -4266,10 +4275,10 @@
         <v>27.3</v>
       </c>
       <c r="AQ16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AS16">
         <v>0</v>
@@ -4278,22 +4287,22 @@
         <v>8</v>
       </c>
       <c r="AU16" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AV16">
         <v>0</v>
       </c>
       <c r="AW16" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AX16">
         <v>8.800000000000001</v>
       </c>
       <c r="AY16" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AZ16">
-        <v>538.3</v>
+        <v>538.8</v>
       </c>
       <c r="BA16">
         <v>5</v>
@@ -4433,286 +4442,286 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="CU1" s="1" t="s">
         <v>49</v>
@@ -4721,16 +4730,16 @@
         <v>48</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:104">
@@ -4747,16 +4756,16 @@
         <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F2" t="s">
         <v>110</v>
       </c>
       <c r="G2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -4789,13 +4798,13 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="V2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="W2">
         <v>0.1167</v>
@@ -4885,10 +4894,10 @@
         <v>128.1</v>
       </c>
       <c r="AZ2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BA2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BB2">
         <v>88.09999999999999</v>
@@ -4975,7 +4984,7 @@
         <v>1.1487</v>
       </c>
       <c r="CD2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE2">
         <v>1974</v>
@@ -5023,13 +5032,13 @@
         <v>2.9</v>
       </c>
       <c r="CT2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU2">
         <v>1.1</v>
       </c>
       <c r="CV2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CX2">
         <v>82.3</v>
@@ -5055,16 +5064,16 @@
         <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -5097,13 +5106,13 @@
         <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U3" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="V3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="W3">
         <v>0.1167</v>
@@ -5193,10 +5202,10 @@
         <v>104.7</v>
       </c>
       <c r="AZ3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="BA3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="BB3">
         <v>83.09999999999999</v>
@@ -5283,7 +5292,7 @@
         <v>1.1499</v>
       </c>
       <c r="CD3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE3">
         <v>1939</v>
@@ -5331,13 +5340,13 @@
         <v>2.7</v>
       </c>
       <c r="CT3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU3">
         <v>1.2</v>
       </c>
       <c r="CV3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CX3">
         <v>81.59999999999999</v>
@@ -5363,16 +5372,16 @@
         <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -5405,13 +5414,13 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U4" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="V4" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="W4">
         <v>0.1167</v>
@@ -5495,16 +5504,16 @@
         <v>4.7</v>
       </c>
       <c r="AX4" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AY4">
         <v>91.40000000000001</v>
       </c>
       <c r="AZ4" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BA4" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BB4">
         <v>81.09999999999999</v>
@@ -5591,7 +5600,7 @@
         <v>1.15</v>
       </c>
       <c r="CD4" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE4">
         <v>1936</v>
@@ -5639,13 +5648,13 @@
         <v>2.6</v>
       </c>
       <c r="CT4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU4">
         <v>1.3</v>
       </c>
       <c r="CV4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CX4">
         <v>81.40000000000001</v>
@@ -5671,16 +5680,16 @@
         <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F5" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -5713,13 +5722,13 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U5" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="V5" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="W5">
         <v>0.1167</v>
@@ -5803,16 +5812,16 @@
         <v>4.7</v>
       </c>
       <c r="AX5" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AY5">
         <v>89.90000000000001</v>
       </c>
       <c r="AZ5" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BA5" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BB5">
         <v>82</v>
@@ -5899,7 +5908,7 @@
         <v>1.1538</v>
       </c>
       <c r="CD5" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE5">
         <v>1823</v>
@@ -5947,13 +5956,13 @@
         <v>2</v>
       </c>
       <c r="CT5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU5">
         <v>1.3</v>
       </c>
       <c r="CV5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CX5">
         <v>79.5</v>
@@ -5979,22 +5988,22 @@
         <v>124</v>
       </c>
       <c r="E6" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F6" t="s">
         <v>111</v>
       </c>
       <c r="G6" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H6" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I6" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J6">
-        <v>692.3</v>
+        <v>692.9</v>
       </c>
       <c r="K6">
         <v>14.2</v>
@@ -6024,13 +6033,13 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U6" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="V6" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="W6">
         <v>0.1667</v>
@@ -6120,10 +6129,10 @@
         <v>218.6</v>
       </c>
       <c r="AZ6" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BA6" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BB6">
         <v>87.8</v>
@@ -6210,7 +6219,7 @@
         <v>1.2005</v>
       </c>
       <c r="CD6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE6">
         <v>502</v>
@@ -6258,13 +6267,13 @@
         <v>18.3</v>
       </c>
       <c r="CT6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU6">
         <v>11</v>
       </c>
       <c r="CV6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW6">
         <v>68</v>
@@ -6293,22 +6302,22 @@
         <v>124</v>
       </c>
       <c r="E7" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F7" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G7" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H7" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I7" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J7">
-        <v>692.3</v>
+        <v>692.9</v>
       </c>
       <c r="K7">
         <v>15.2</v>
@@ -6338,13 +6347,13 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U7" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="V7" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="W7">
         <v>0.1667</v>
@@ -6371,7 +6380,7 @@
         <v>-1.6</v>
       </c>
       <c r="AE7" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AF7">
         <v>68.3</v>
@@ -6434,10 +6443,10 @@
         <v>218.8</v>
       </c>
       <c r="AZ7" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BA7" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BB7">
         <v>88.59999999999999</v>
@@ -6524,7 +6533,7 @@
         <v>1.1988</v>
       </c>
       <c r="CD7" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE7">
         <v>571</v>
@@ -6572,13 +6581,13 @@
         <v>12.1</v>
       </c>
       <c r="CT7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU7">
         <v>3.7</v>
       </c>
       <c r="CV7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW7">
         <v>69</v>
@@ -6607,22 +6616,22 @@
         <v>124</v>
       </c>
       <c r="E8" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F8" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G8" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H8" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J8">
-        <v>692.3</v>
+        <v>692.9</v>
       </c>
       <c r="K8">
         <v>16.2</v>
@@ -6652,13 +6661,13 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U8" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="V8" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="W8">
         <v>0.1667</v>
@@ -6748,10 +6757,10 @@
         <v>229.3</v>
       </c>
       <c r="AZ8" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BA8" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BB8">
         <v>91.7</v>
@@ -6838,7 +6847,7 @@
         <v>1.196</v>
       </c>
       <c r="CD8" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE8">
         <v>665</v>
@@ -6886,13 +6895,13 @@
         <v>9.1</v>
       </c>
       <c r="CT8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU8">
         <v>4</v>
       </c>
       <c r="CV8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW8">
         <v>71</v>
@@ -6921,22 +6930,22 @@
         <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F9" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G9" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H9" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I9" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J9">
-        <v>692.3</v>
+        <v>692.9</v>
       </c>
       <c r="K9">
         <v>17.2</v>
@@ -6966,13 +6975,13 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U9" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="V9" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="W9">
         <v>0.1667</v>
@@ -7062,10 +7071,10 @@
         <v>232.3</v>
       </c>
       <c r="AZ9" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BA9" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BB9">
         <v>94.5</v>
@@ -7152,7 +7161,7 @@
         <v>1.1962</v>
       </c>
       <c r="CD9" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE9">
         <v>669</v>
@@ -7200,13 +7209,13 @@
         <v>7.3</v>
       </c>
       <c r="CT9" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU9">
         <v>5.4</v>
       </c>
       <c r="CV9" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW9">
         <v>70</v>
@@ -7235,22 +7244,22 @@
         <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F10" t="s">
         <v>112</v>
       </c>
       <c r="G10" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I10" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J10">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="K10">
         <v>14.2</v>
@@ -7280,13 +7289,13 @@
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U10" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="V10" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="W10">
         <v>0.1667</v>
@@ -7295,7 +7304,7 @@
         <v>6.3</v>
       </c>
       <c r="Y10">
-        <v>90.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="Z10">
         <v>53</v>
@@ -7376,10 +7385,10 @@
         <v>252.9</v>
       </c>
       <c r="AZ10" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="BA10" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="BB10">
         <v>97</v>
@@ -7466,7 +7475,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD10" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE10">
         <v>858</v>
@@ -7514,13 +7523,13 @@
         <v>0</v>
       </c>
       <c r="CT10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="CU10">
         <v>12.2</v>
       </c>
       <c r="CV10" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW10">
         <v>86</v>
@@ -7549,22 +7558,22 @@
         <v>125</v>
       </c>
       <c r="E11" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F11" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J11">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="K11">
         <v>15.2</v>
@@ -7594,13 +7603,13 @@
         <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U11" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="V11" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="W11">
         <v>0.1667</v>
@@ -7690,10 +7699,10 @@
         <v>262.6</v>
       </c>
       <c r="AZ11" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="BA11" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="BB11">
         <v>97.09999999999999</v>
@@ -7780,7 +7789,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD11" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE11">
         <v>858</v>
@@ -7828,13 +7837,13 @@
         <v>0</v>
       </c>
       <c r="CT11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="CU11">
         <v>11.1</v>
       </c>
       <c r="CV11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW11">
         <v>85</v>
@@ -7863,22 +7872,22 @@
         <v>125</v>
       </c>
       <c r="E12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F12" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G12" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H12" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I12" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J12">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="K12">
         <v>16.2</v>
@@ -7908,13 +7917,13 @@
         <v>0</v>
       </c>
       <c r="T12" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U12" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="V12" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="W12">
         <v>0.1667</v>
@@ -7941,7 +7950,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AF12">
         <v>83.8</v>
@@ -8004,10 +8013,10 @@
         <v>263</v>
       </c>
       <c r="AZ12" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="BA12" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="BB12">
         <v>98.5</v>
@@ -8094,7 +8103,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD12" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE12">
         <v>858</v>
@@ -8142,13 +8151,13 @@
         <v>0</v>
       </c>
       <c r="CT12" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="CU12">
         <v>11.5</v>
       </c>
       <c r="CV12" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW12">
         <v>84</v>
@@ -8177,22 +8186,22 @@
         <v>125</v>
       </c>
       <c r="E13" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F13" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G13" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H13" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I13" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J13">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="K13">
         <v>17.2</v>
@@ -8222,13 +8231,13 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U13" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="V13" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="W13">
         <v>0.1667</v>
@@ -8318,10 +8327,10 @@
         <v>260.5</v>
       </c>
       <c r="AZ13" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="BA13" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="BB13">
         <v>90.40000000000001</v>
@@ -8408,7 +8417,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD13" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE13">
         <v>858</v>
@@ -8456,13 +8465,13 @@
         <v>0</v>
       </c>
       <c r="CT13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="CU13">
         <v>17.7</v>
       </c>
       <c r="CV13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW13">
         <v>84</v>
@@ -8491,22 +8500,22 @@
         <v>126</v>
       </c>
       <c r="E14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F14" t="s">
         <v>112</v>
       </c>
       <c r="G14" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="H14" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I14" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J14">
-        <v>219.8</v>
+        <v>220.4</v>
       </c>
       <c r="K14">
         <v>14.2</v>
@@ -8536,13 +8545,13 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U14" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="V14" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="W14">
         <v>0.1667</v>
@@ -8632,10 +8641,10 @@
         <v>172.5</v>
       </c>
       <c r="AZ14" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BA14" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BB14">
         <v>91.7</v>
@@ -8722,7 +8731,7 @@
         <v>1.1547</v>
       </c>
       <c r="CD14" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE14">
         <v>1802</v>
@@ -8770,13 +8779,13 @@
         <v>2</v>
       </c>
       <c r="CT14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU14">
         <v>20.5</v>
       </c>
       <c r="CV14" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="CW14">
         <v>88</v>
@@ -8805,22 +8814,22 @@
         <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F15" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G15" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="H15" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I15" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J15">
-        <v>219.8</v>
+        <v>220.4</v>
       </c>
       <c r="K15">
         <v>15.2</v>
@@ -8850,13 +8859,13 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U15" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="V15" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="W15">
         <v>0.1667</v>
@@ -8946,10 +8955,10 @@
         <v>172.6</v>
       </c>
       <c r="AZ15" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BA15" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BB15">
         <v>93.2</v>
@@ -9036,7 +9045,7 @@
         <v>1.1576</v>
       </c>
       <c r="CD15" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE15">
         <v>1695</v>
@@ -9084,13 +9093,13 @@
         <v>2.5</v>
       </c>
       <c r="CT15" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU15">
         <v>22.7</v>
       </c>
       <c r="CV15" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="CW15">
         <v>87</v>
@@ -9119,22 +9128,22 @@
         <v>126</v>
       </c>
       <c r="E16" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F16" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G16" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="H16" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I16" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J16">
-        <v>219.8</v>
+        <v>220.4</v>
       </c>
       <c r="K16">
         <v>16.2</v>
@@ -9164,13 +9173,13 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U16" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="V16" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="W16">
         <v>0.1667</v>
@@ -9260,10 +9269,10 @@
         <v>172.4</v>
       </c>
       <c r="AZ16" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BA16" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BB16">
         <v>94.40000000000001</v>
@@ -9350,7 +9359,7 @@
         <v>1.1605</v>
       </c>
       <c r="CD16" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE16">
         <v>1596</v>
@@ -9398,13 +9407,13 @@
         <v>2.8</v>
       </c>
       <c r="CT16" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU16">
         <v>25.7</v>
       </c>
       <c r="CV16" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="CW16">
         <v>86</v>
@@ -9433,22 +9442,22 @@
         <v>126</v>
       </c>
       <c r="E17" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F17" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G17" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="H17" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J17">
-        <v>219.8</v>
+        <v>220.4</v>
       </c>
       <c r="K17">
         <v>17.2</v>
@@ -9478,13 +9487,13 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="V17" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="W17">
         <v>0.1667</v>
@@ -9574,10 +9583,10 @@
         <v>170</v>
       </c>
       <c r="AZ17" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BA17" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BB17">
         <v>94.5</v>
@@ -9664,7 +9673,7 @@
         <v>1.1647</v>
       </c>
       <c r="CD17" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE17">
         <v>1457</v>
@@ -9712,13 +9721,13 @@
         <v>3.6</v>
       </c>
       <c r="CT17" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU17">
         <v>24.1</v>
       </c>
       <c r="CV17" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="CW17">
         <v>84</v>
@@ -9747,22 +9756,22 @@
         <v>127</v>
       </c>
       <c r="E18" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F18" t="s">
         <v>113</v>
       </c>
       <c r="G18" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H18" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I18" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="J18">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="K18">
         <v>16.7</v>
@@ -9792,13 +9801,13 @@
         <v>100</v>
       </c>
       <c r="T18" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U18" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="V18" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="W18">
         <v>0.6667</v>
@@ -9888,10 +9897,10 @@
         <v>154.2</v>
       </c>
       <c r="AZ18" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BA18" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BB18">
         <v>89.09999999999999</v>
@@ -9978,7 +9987,7 @@
         <v>1.132</v>
       </c>
       <c r="CD18" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE18">
         <v>2351</v>
@@ -10026,13 +10035,13 @@
         <v>63.3</v>
       </c>
       <c r="CT18" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="CU18">
         <v>12.6</v>
       </c>
       <c r="CV18" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW18">
         <v>78</v>
@@ -10061,22 +10070,22 @@
         <v>127</v>
       </c>
       <c r="E19" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F19" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G19" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H19" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I19" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="J19">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="K19">
         <v>17.7</v>
@@ -10106,13 +10115,13 @@
         <v>100</v>
       </c>
       <c r="T19" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U19" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="V19" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="W19">
         <v>0.6667</v>
@@ -10139,7 +10148,7 @@
         <v>2.2</v>
       </c>
       <c r="AE19" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AF19">
         <v>77.2</v>
@@ -10202,10 +10211,10 @@
         <v>146.3</v>
       </c>
       <c r="AZ19" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BA19" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BB19">
         <v>92.59999999999999</v>
@@ -10292,7 +10301,7 @@
         <v>1.134</v>
       </c>
       <c r="CD19" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE19">
         <v>2298</v>
@@ -10340,13 +10349,13 @@
         <v>58.5</v>
       </c>
       <c r="CT19" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="CU19">
         <v>12.9</v>
       </c>
       <c r="CV19" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW19">
         <v>77</v>
@@ -10375,22 +10384,22 @@
         <v>127</v>
       </c>
       <c r="E20" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F20" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G20" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H20" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I20" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="J20">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="K20">
         <v>18.7</v>
@@ -10420,13 +10429,13 @@
         <v>100</v>
       </c>
       <c r="T20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U20" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="V20" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="W20">
         <v>0.6667</v>
@@ -10516,10 +10525,10 @@
         <v>160.5</v>
       </c>
       <c r="AZ20" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BA20" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BB20">
         <v>89.40000000000001</v>
@@ -10606,7 +10615,7 @@
         <v>1.1379</v>
       </c>
       <c r="CD20" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE20">
         <v>2182</v>
@@ -10654,13 +10663,13 @@
         <v>49.1</v>
       </c>
       <c r="CT20" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="CU20">
         <v>14.6</v>
       </c>
       <c r="CV20" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW20">
         <v>75</v>
@@ -10689,22 +10698,22 @@
         <v>127</v>
       </c>
       <c r="E21" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F21" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H21" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I21" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="J21">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="K21">
         <v>19.7</v>
@@ -10734,13 +10743,13 @@
         <v>100</v>
       </c>
       <c r="T21" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U21" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="V21" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="W21">
         <v>0.6667</v>
@@ -10830,10 +10839,10 @@
         <v>159.2</v>
       </c>
       <c r="AZ21" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BA21" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BB21">
         <v>86.8</v>
@@ -10920,7 +10929,7 @@
         <v>1.1414</v>
       </c>
       <c r="CD21" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE21">
         <v>2083</v>
@@ -10968,13 +10977,13 @@
         <v>46.6</v>
       </c>
       <c r="CT21" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="CU21">
         <v>13.2</v>
       </c>
       <c r="CV21" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW21">
         <v>73</v>
@@ -11003,22 +11012,22 @@
         <v>128</v>
       </c>
       <c r="E22" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F22" t="s">
         <v>114</v>
       </c>
       <c r="G22" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H22" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="I22" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="J22">
-        <v>185.8</v>
+        <v>186.4</v>
       </c>
       <c r="K22">
         <v>17.1</v>
@@ -11048,13 +11057,13 @@
         <v>0</v>
       </c>
       <c r="T22" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U22" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="V22" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="W22">
         <v>0.0833</v>
@@ -11144,10 +11153,10 @@
         <v>164</v>
       </c>
       <c r="AZ22" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="BA22" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="BB22">
         <v>91.7</v>
@@ -11234,7 +11243,7 @@
         <v>1.1538</v>
       </c>
       <c r="CD22" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE22">
         <v>1829</v>
@@ -11282,13 +11291,13 @@
         <v>1.3</v>
       </c>
       <c r="CT22" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU22">
         <v>9.699999999999999</v>
       </c>
       <c r="CV22" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW22">
         <v>84</v>
@@ -11317,22 +11326,22 @@
         <v>128</v>
       </c>
       <c r="E23" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F23" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G23" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H23" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="I23" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="J23">
-        <v>185.8</v>
+        <v>186.4</v>
       </c>
       <c r="K23">
         <v>18.1</v>
@@ -11362,13 +11371,13 @@
         <v>0</v>
       </c>
       <c r="T23" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U23" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="V23" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="W23">
         <v>0.0833</v>
@@ -11458,10 +11467,10 @@
         <v>164.5</v>
       </c>
       <c r="AZ23" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="BA23" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="BB23">
         <v>89.90000000000001</v>
@@ -11548,7 +11557,7 @@
         <v>1.1586</v>
       </c>
       <c r="CD23" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE23">
         <v>1671</v>
@@ -11596,13 +11605,13 @@
         <v>1.2</v>
       </c>
       <c r="CT23" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU23">
         <v>8.6</v>
       </c>
       <c r="CV23" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW23">
         <v>82</v>
@@ -11631,22 +11640,22 @@
         <v>128</v>
       </c>
       <c r="E24" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F24" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G24" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H24" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="I24" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="J24">
-        <v>185.8</v>
+        <v>186.4</v>
       </c>
       <c r="K24">
         <v>19.1</v>
@@ -11676,13 +11685,13 @@
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U24" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="V24" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="W24">
         <v>0.0833</v>
@@ -11772,10 +11781,10 @@
         <v>169.5</v>
       </c>
       <c r="AZ24" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BA24" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BB24">
         <v>93</v>
@@ -11862,7 +11871,7 @@
         <v>1.1626</v>
       </c>
       <c r="CD24" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE24">
         <v>1526</v>
@@ -11910,13 +11919,13 @@
         <v>2.6</v>
       </c>
       <c r="CT24" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU24">
         <v>5.1</v>
       </c>
       <c r="CV24" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW24">
         <v>80</v>
@@ -11945,22 +11954,22 @@
         <v>128</v>
       </c>
       <c r="E25" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F25" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G25" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H25" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="I25" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="J25">
-        <v>185.8</v>
+        <v>186.4</v>
       </c>
       <c r="K25">
         <v>20.1</v>
@@ -11990,13 +11999,13 @@
         <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U25" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="V25" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="W25">
         <v>0.0833</v>
@@ -12086,10 +12095,10 @@
         <v>168.8</v>
       </c>
       <c r="AZ25" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="BA25" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="BB25">
         <v>89.2</v>
@@ -12176,7 +12185,7 @@
         <v>1.1644</v>
       </c>
       <c r="CD25" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE25">
         <v>1461</v>
@@ -12224,13 +12233,13 @@
         <v>4.1</v>
       </c>
       <c r="CT25" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU25">
         <v>6.8</v>
       </c>
       <c r="CV25" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW25">
         <v>79</v>
@@ -12259,22 +12268,22 @@
         <v>129</v>
       </c>
       <c r="E26" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F26" t="s">
         <v>115</v>
       </c>
       <c r="G26" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H26" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I26" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J26">
-        <v>17.9</v>
+        <v>18.5</v>
       </c>
       <c r="K26">
         <v>17.2</v>
@@ -12304,13 +12313,13 @@
         <v>18.8</v>
       </c>
       <c r="T26" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U26" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="V26" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="W26">
         <v>0.1667</v>
@@ -12400,10 +12409,10 @@
         <v>275.8</v>
       </c>
       <c r="AZ26" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="BA26" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="BB26">
         <v>84.5</v>
@@ -12490,7 +12499,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD26" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE26">
         <v>858</v>
@@ -12538,13 +12547,13 @@
         <v>0</v>
       </c>
       <c r="CT26" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="CU26">
         <v>11.1</v>
       </c>
       <c r="CV26" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW26">
         <v>99</v>
@@ -12573,22 +12582,22 @@
         <v>129</v>
       </c>
       <c r="E27" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F27" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G27" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H27" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I27" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J27">
-        <v>17.9</v>
+        <v>18.5</v>
       </c>
       <c r="K27">
         <v>18.2</v>
@@ -12618,13 +12627,13 @@
         <v>75</v>
       </c>
       <c r="T27" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U27" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="V27" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="W27">
         <v>0.1667</v>
@@ -12714,10 +12723,10 @@
         <v>259.4</v>
       </c>
       <c r="AZ27" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="BA27" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="BB27">
         <v>81.5</v>
@@ -12804,7 +12813,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD27" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE27">
         <v>858</v>
@@ -12852,13 +12861,13 @@
         <v>0</v>
       </c>
       <c r="CT27" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="CU27">
         <v>14.5</v>
       </c>
       <c r="CV27" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW27">
         <v>98</v>
@@ -12887,22 +12896,22 @@
         <v>129</v>
       </c>
       <c r="E28" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F28" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G28" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H28" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I28" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J28">
-        <v>17.9</v>
+        <v>18.5</v>
       </c>
       <c r="K28">
         <v>19.2</v>
@@ -12932,13 +12941,13 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U28" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="V28" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="W28">
         <v>0.1667</v>
@@ -13028,10 +13037,10 @@
         <v>241.1</v>
       </c>
       <c r="AZ28" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="BA28" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="BB28">
         <v>82.3</v>
@@ -13118,7 +13127,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD28" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE28">
         <v>858</v>
@@ -13166,13 +13175,13 @@
         <v>0</v>
       </c>
       <c r="CT28" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="CU28">
         <v>28</v>
       </c>
       <c r="CV28" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="CW28">
         <v>97</v>
@@ -13201,22 +13210,22 @@
         <v>129</v>
       </c>
       <c r="E29" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F29" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G29" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H29" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I29" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J29">
-        <v>17.9</v>
+        <v>18.5</v>
       </c>
       <c r="K29">
         <v>20.2</v>
@@ -13246,13 +13255,13 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U29" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="V29" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="W29">
         <v>0.1667</v>
@@ -13342,10 +13351,10 @@
         <v>232.7</v>
       </c>
       <c r="AZ29" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="BA29" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="BB29">
         <v>80.40000000000001</v>
@@ -13432,7 +13441,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD29" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE29">
         <v>858</v>
@@ -13480,13 +13489,13 @@
         <v>0</v>
       </c>
       <c r="CT29" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="CU29">
         <v>23.2</v>
       </c>
       <c r="CV29" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="CW29">
         <v>93</v>
@@ -13515,22 +13524,22 @@
         <v>130</v>
       </c>
       <c r="E30" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F30" t="s">
         <v>116</v>
       </c>
       <c r="G30" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H30" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I30" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="J30">
-        <v>597.2</v>
+        <v>597.8</v>
       </c>
       <c r="K30">
         <v>17.3</v>
@@ -13560,13 +13569,13 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U30" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="V30" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="W30">
         <v>0.25</v>
@@ -13656,10 +13665,10 @@
         <v>108.6</v>
       </c>
       <c r="AZ30" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BA30" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BB30">
         <v>88.90000000000001</v>
@@ -13746,7 +13755,7 @@
         <v>1.1416</v>
       </c>
       <c r="CD30" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE30">
         <v>2178</v>
@@ -13794,13 +13803,13 @@
         <v>15.9</v>
       </c>
       <c r="CT30" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU30">
         <v>3</v>
       </c>
       <c r="CV30" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW30">
         <v>80</v>
@@ -13829,22 +13838,22 @@
         <v>130</v>
       </c>
       <c r="E31" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F31" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G31" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H31" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I31" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="J31">
-        <v>597.2</v>
+        <v>597.8</v>
       </c>
       <c r="K31">
         <v>18.3</v>
@@ -13874,13 +13883,13 @@
         <v>56.2</v>
       </c>
       <c r="T31" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U31" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="V31" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="W31">
         <v>0.25</v>
@@ -13907,7 +13916,7 @@
         <v>0.3</v>
       </c>
       <c r="AE31" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AF31">
         <v>78.59999999999999</v>
@@ -13964,16 +13973,16 @@
         <v>5.3</v>
       </c>
       <c r="AX31" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AY31">
         <v>92.40000000000001</v>
       </c>
       <c r="AZ31" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="BA31" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="BB31">
         <v>35</v>
@@ -14060,7 +14069,7 @@
         <v>1.1448</v>
       </c>
       <c r="CD31" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE31">
         <v>2061</v>
@@ -14108,13 +14117,13 @@
         <v>27.6</v>
       </c>
       <c r="CT31" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="CU31">
         <v>19</v>
       </c>
       <c r="CV31" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="CW31">
         <v>79</v>
@@ -14143,22 +14152,22 @@
         <v>130</v>
       </c>
       <c r="E32" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F32" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G32" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H32" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I32" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="J32">
-        <v>597.2</v>
+        <v>597.8</v>
       </c>
       <c r="K32">
         <v>19.3</v>
@@ -14188,13 +14197,13 @@
         <v>56.2</v>
       </c>
       <c r="T32" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U32" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="V32" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="W32">
         <v>0.25</v>
@@ -14284,10 +14293,10 @@
         <v>72.5</v>
       </c>
       <c r="AZ32" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BA32" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BB32">
         <v>65.3</v>
@@ -14374,7 +14383,7 @@
         <v>1.1486</v>
       </c>
       <c r="CD32" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE32">
         <v>1937</v>
@@ -14422,13 +14431,13 @@
         <v>24.2</v>
       </c>
       <c r="CT32" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="CU32">
         <v>14.5</v>
       </c>
       <c r="CV32" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW32">
         <v>77</v>
@@ -14457,22 +14466,22 @@
         <v>130</v>
       </c>
       <c r="E33" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F33" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G33" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H33" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I33" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="J33">
-        <v>597.2</v>
+        <v>597.8</v>
       </c>
       <c r="K33">
         <v>20.3</v>
@@ -14502,13 +14511,13 @@
         <v>56.2</v>
       </c>
       <c r="T33" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U33" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="V33" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="W33">
         <v>0.25</v>
@@ -14592,16 +14601,16 @@
         <v>8.9</v>
       </c>
       <c r="AX33" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AY33">
         <v>82.40000000000001</v>
       </c>
       <c r="AZ33" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BA33" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BB33">
         <v>67.2</v>
@@ -14688,7 +14697,7 @@
         <v>1.1506</v>
       </c>
       <c r="CD33" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE33">
         <v>1875</v>
@@ -14736,13 +14745,13 @@
         <v>21</v>
       </c>
       <c r="CT33" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="CU33">
         <v>12.8</v>
       </c>
       <c r="CV33" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW33">
         <v>76</v>
@@ -14771,22 +14780,22 @@
         <v>131</v>
       </c>
       <c r="E34" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F34" t="s">
         <v>116</v>
       </c>
       <c r="G34" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H34" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="I34" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="J34">
-        <v>71.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="K34">
         <v>17.3</v>
@@ -14816,13 +14825,13 @@
         <v>100</v>
       </c>
       <c r="T34" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U34" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="V34" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="W34">
         <v>0.25</v>
@@ -14912,10 +14921,10 @@
         <v>185</v>
       </c>
       <c r="AZ34" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BA34" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BB34">
         <v>82.40000000000001</v>
@@ -15002,7 +15011,7 @@
         <v>1.121</v>
       </c>
       <c r="CD34" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE34">
         <v>2668</v>
@@ -15050,13 +15059,13 @@
         <v>41.7</v>
       </c>
       <c r="CT34" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="CU34">
         <v>23.2</v>
       </c>
       <c r="CV34" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="CW34">
         <v>78</v>
@@ -15085,22 +15094,22 @@
         <v>131</v>
       </c>
       <c r="E35" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F35" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G35" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H35" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="I35" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="J35">
-        <v>71.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="K35">
         <v>18.3</v>
@@ -15130,13 +15139,13 @@
         <v>100</v>
       </c>
       <c r="T35" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U35" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="V35" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="W35">
         <v>0.25</v>
@@ -15226,10 +15235,10 @@
         <v>184.6</v>
       </c>
       <c r="AZ35" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BA35" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BB35">
         <v>83.40000000000001</v>
@@ -15316,7 +15325,7 @@
         <v>1.1238</v>
       </c>
       <c r="CD35" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE35">
         <v>2584</v>
@@ -15364,13 +15373,13 @@
         <v>46.7</v>
       </c>
       <c r="CT35" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="CU35">
         <v>21.4</v>
       </c>
       <c r="CV35" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="CW35">
         <v>77</v>
@@ -15399,22 +15408,22 @@
         <v>131</v>
       </c>
       <c r="E36" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F36" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G36" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H36" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="I36" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="J36">
-        <v>71.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="K36">
         <v>19.3</v>
@@ -15444,13 +15453,13 @@
         <v>100</v>
       </c>
       <c r="T36" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U36" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="V36" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="W36">
         <v>0.25</v>
@@ -15477,7 +15486,7 @@
         <v>0.6</v>
       </c>
       <c r="AE36" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AF36">
         <v>76.90000000000001</v>
@@ -15540,10 +15549,10 @@
         <v>176.9</v>
       </c>
       <c r="AZ36" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BA36" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BB36">
         <v>90</v>
@@ -15630,7 +15639,7 @@
         <v>1.1268</v>
       </c>
       <c r="CD36" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE36">
         <v>2500</v>
@@ -15678,13 +15687,13 @@
         <v>53.8</v>
       </c>
       <c r="CT36" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="CU36">
         <v>19.8</v>
       </c>
       <c r="CV36" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="CW36">
         <v>76</v>
@@ -15713,22 +15722,22 @@
         <v>131</v>
       </c>
       <c r="E37" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F37" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G37" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H37" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="I37" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="J37">
-        <v>71.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="K37">
         <v>20.3</v>
@@ -15758,13 +15767,13 @@
         <v>100</v>
       </c>
       <c r="T37" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U37" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="V37" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="W37">
         <v>0.25</v>
@@ -15791,7 +15800,7 @@
         <v>0.6</v>
       </c>
       <c r="AE37" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AF37">
         <v>76</v>
@@ -15854,10 +15863,10 @@
         <v>177.7</v>
       </c>
       <c r="AZ37" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BA37" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="BB37">
         <v>90.59999999999999</v>
@@ -15944,7 +15953,7 @@
         <v>1.1294</v>
       </c>
       <c r="CD37" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE37">
         <v>2420</v>
@@ -15992,13 +16001,13 @@
         <v>57.1</v>
       </c>
       <c r="CT37" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="CU37">
         <v>12.6</v>
       </c>
       <c r="CV37" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW37">
         <v>75</v>
@@ -16027,22 +16036,22 @@
         <v>132</v>
       </c>
       <c r="E38" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F38" t="s">
         <v>117</v>
       </c>
       <c r="G38" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="H38" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I38" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="J38">
-        <v>257.6</v>
+        <v>258.2</v>
       </c>
       <c r="K38">
         <v>17.3</v>
@@ -16072,13 +16081,13 @@
         <v>100</v>
       </c>
       <c r="T38" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U38" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="V38" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="W38">
         <v>0.25</v>
@@ -16168,10 +16177,10 @@
         <v>32.7</v>
       </c>
       <c r="AZ38" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="BA38" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="BB38">
         <v>75.8</v>
@@ -16258,7 +16267,7 @@
         <v>1.1758</v>
       </c>
       <c r="CD38" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE38">
         <v>1119</v>
@@ -16306,13 +16315,13 @@
         <v>41.4</v>
       </c>
       <c r="CT38" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="CU38">
         <v>16.7</v>
       </c>
       <c r="CV38" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW38">
         <v>70</v>
@@ -16341,22 +16350,22 @@
         <v>132</v>
       </c>
       <c r="E39" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F39" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G39" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="H39" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I39" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="J39">
-        <v>257.6</v>
+        <v>258.2</v>
       </c>
       <c r="K39">
         <v>18.3</v>
@@ -16386,13 +16395,13 @@
         <v>100</v>
       </c>
       <c r="T39" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U39" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="V39" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="W39">
         <v>0.25</v>
@@ -16419,7 +16428,7 @@
         <v>1.8</v>
       </c>
       <c r="AE39" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AF39">
         <v>70.09999999999999</v>
@@ -16482,10 +16491,10 @@
         <v>33.1</v>
       </c>
       <c r="AZ39" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="BA39" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="BB39">
         <v>71.59999999999999</v>
@@ -16572,7 +16581,7 @@
         <v>1.1761</v>
       </c>
       <c r="CD39" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE39">
         <v>1111</v>
@@ -16620,13 +16629,13 @@
         <v>41.2</v>
       </c>
       <c r="CT39" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="CU39">
         <v>14.7</v>
       </c>
       <c r="CV39" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW39">
         <v>70</v>
@@ -16655,22 +16664,22 @@
         <v>132</v>
       </c>
       <c r="E40" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F40" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G40" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="H40" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I40" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="J40">
-        <v>257.6</v>
+        <v>258.2</v>
       </c>
       <c r="K40">
         <v>19.3</v>
@@ -16700,13 +16709,13 @@
         <v>100</v>
       </c>
       <c r="T40" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U40" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="V40" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="W40">
         <v>0.25</v>
@@ -16790,16 +16799,16 @@
         <v>12.6</v>
       </c>
       <c r="AX40" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AY40">
         <v>35.2</v>
       </c>
       <c r="AZ40" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="BA40" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="BB40">
         <v>69.8</v>
@@ -16886,7 +16895,7 @@
         <v>1.1766</v>
       </c>
       <c r="CD40" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE40">
         <v>1101</v>
@@ -16934,13 +16943,13 @@
         <v>36.2</v>
       </c>
       <c r="CT40" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="CU40">
         <v>13.3</v>
       </c>
       <c r="CV40" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW40">
         <v>70</v>
@@ -16969,22 +16978,22 @@
         <v>132</v>
       </c>
       <c r="E41" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F41" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G41" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="H41" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I41" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="J41">
-        <v>257.6</v>
+        <v>258.2</v>
       </c>
       <c r="K41">
         <v>20.3</v>
@@ -17014,13 +17023,13 @@
         <v>100</v>
       </c>
       <c r="T41" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U41" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="V41" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="W41">
         <v>0.25</v>
@@ -17047,7 +17056,7 @@
         <v>1.8</v>
       </c>
       <c r="AE41" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AF41">
         <v>69.90000000000001</v>
@@ -17104,16 +17113,16 @@
         <v>13.1</v>
       </c>
       <c r="AX41" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AY41">
         <v>34.6</v>
       </c>
       <c r="AZ41" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="BA41" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="BB41">
         <v>68.7</v>
@@ -17200,7 +17209,7 @@
         <v>1.1771</v>
       </c>
       <c r="CD41" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE41">
         <v>1089</v>
@@ -17248,13 +17257,13 @@
         <v>47</v>
       </c>
       <c r="CT41" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="CU41">
         <v>12.6</v>
       </c>
       <c r="CV41" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW41">
         <v>70</v>
@@ -17283,22 +17292,22 @@
         <v>133</v>
       </c>
       <c r="E42" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F42" t="s">
         <v>118</v>
       </c>
       <c r="G42" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H42" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I42" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J42">
-        <v>207.5</v>
+        <v>208.1</v>
       </c>
       <c r="K42">
         <v>18.2</v>
@@ -17328,13 +17337,13 @@
         <v>100</v>
       </c>
       <c r="T42" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U42" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="V42" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="W42">
         <v>0.1667</v>
@@ -17424,10 +17433,10 @@
         <v>69.2</v>
       </c>
       <c r="AZ42" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BA42" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BB42">
         <v>84.7</v>
@@ -17514,7 +17523,7 @@
         <v>0.9573</v>
       </c>
       <c r="CD42" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="CE42">
         <v>8275</v>
@@ -17562,13 +17571,13 @@
         <v>0.4</v>
       </c>
       <c r="CT42" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU42">
         <v>4.1</v>
       </c>
       <c r="CV42" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW42">
         <v>93</v>
@@ -17597,22 +17606,22 @@
         <v>133</v>
       </c>
       <c r="E43" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F43" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G43" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H43" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I43" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J43">
-        <v>207.5</v>
+        <v>208.1</v>
       </c>
       <c r="K43">
         <v>19.2</v>
@@ -17642,13 +17651,13 @@
         <v>25</v>
       </c>
       <c r="T43" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U43" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="V43" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="W43">
         <v>0.1667</v>
@@ -17732,16 +17741,16 @@
         <v>7.9</v>
       </c>
       <c r="AX43" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AY43">
         <v>85.59999999999999</v>
       </c>
       <c r="AZ43" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BA43" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BB43">
         <v>85.09999999999999</v>
@@ -17828,7 +17837,7 @@
         <v>0.9596</v>
       </c>
       <c r="CD43" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="CE43">
         <v>8176</v>
@@ -17876,13 +17885,13 @@
         <v>0.6</v>
       </c>
       <c r="CT43" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU43">
         <v>7.4</v>
       </c>
       <c r="CV43" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW43">
         <v>92</v>
@@ -17911,22 +17920,22 @@
         <v>133</v>
       </c>
       <c r="E44" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F44" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G44" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H44" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I44" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J44">
-        <v>207.5</v>
+        <v>208.1</v>
       </c>
       <c r="K44">
         <v>20.2</v>
@@ -17956,13 +17965,13 @@
         <v>25</v>
       </c>
       <c r="T44" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U44" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="V44" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="W44">
         <v>0.1667</v>
@@ -18052,10 +18061,10 @@
         <v>101.5</v>
       </c>
       <c r="AZ44" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BA44" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="BB44">
         <v>87.90000000000001</v>
@@ -18142,7 +18151,7 @@
         <v>0.9646</v>
       </c>
       <c r="CD44" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="CE44">
         <v>7989</v>
@@ -18190,13 +18199,13 @@
         <v>1</v>
       </c>
       <c r="CT44" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU44">
         <v>12.4</v>
       </c>
       <c r="CV44" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW44">
         <v>90</v>
@@ -18225,22 +18234,22 @@
         <v>133</v>
       </c>
       <c r="E45" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F45" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G45" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H45" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I45" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J45">
-        <v>207.5</v>
+        <v>208.1</v>
       </c>
       <c r="K45">
         <v>21.2</v>
@@ -18270,13 +18279,13 @@
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U45" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="V45" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="W45">
         <v>0.1667</v>
@@ -18285,7 +18294,7 @@
         <v>10.7</v>
       </c>
       <c r="Y45">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="Z45">
         <v>75.90000000000001</v>
@@ -18366,10 +18375,10 @@
         <v>118.9</v>
       </c>
       <c r="AZ45" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="BA45" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="BB45">
         <v>78.3</v>
@@ -18456,7 +18465,7 @@
         <v>0.9712</v>
       </c>
       <c r="CD45" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="CE45">
         <v>7737</v>
@@ -18504,13 +18513,13 @@
         <v>1.4</v>
       </c>
       <c r="CT45" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU45">
         <v>17.7</v>
       </c>
       <c r="CV45" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW45">
         <v>86</v>
@@ -18539,22 +18548,22 @@
         <v>134</v>
       </c>
       <c r="E46" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F46" t="s">
         <v>119</v>
       </c>
       <c r="G46" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="H46" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I46" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J46">
-        <v>112.4</v>
+        <v>113</v>
       </c>
       <c r="K46">
         <v>18.7</v>
@@ -18584,13 +18593,13 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U46" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="V46" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="W46">
         <v>0.6667</v>
@@ -18680,10 +18689,10 @@
         <v>234.6</v>
       </c>
       <c r="AZ46" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="BA46" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="BB46">
         <v>91.09999999999999</v>
@@ -18770,7 +18779,7 @@
         <v>1.1714</v>
       </c>
       <c r="CD46" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE46">
         <v>1264</v>
@@ -18818,13 +18827,13 @@
         <v>0</v>
       </c>
       <c r="CT46" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU46">
         <v>10.6</v>
       </c>
       <c r="CV46" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW46">
         <v>79</v>
@@ -18853,22 +18862,22 @@
         <v>134</v>
       </c>
       <c r="E47" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F47" t="s">
         <v>122</v>
       </c>
       <c r="G47" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="H47" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I47" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J47">
-        <v>112.4</v>
+        <v>113</v>
       </c>
       <c r="K47">
         <v>19.7</v>
@@ -18898,13 +18907,13 @@
         <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U47" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="V47" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="W47">
         <v>0.6667</v>
@@ -18994,10 +19003,10 @@
         <v>250.6</v>
       </c>
       <c r="AZ47" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="BA47" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="BB47">
         <v>94.59999999999999</v>
@@ -19084,7 +19093,7 @@
         <v>1.176</v>
       </c>
       <c r="CD47" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE47">
         <v>1130</v>
@@ -19132,13 +19141,13 @@
         <v>0</v>
       </c>
       <c r="CT47" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU47">
         <v>7.7</v>
       </c>
       <c r="CV47" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW47">
         <v>76</v>
@@ -19167,22 +19176,22 @@
         <v>134</v>
       </c>
       <c r="E48" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F48" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G48" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="H48" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I48" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J48">
-        <v>112.4</v>
+        <v>113</v>
       </c>
       <c r="K48">
         <v>20.7</v>
@@ -19212,13 +19221,13 @@
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U48" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="V48" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="W48">
         <v>0.6667</v>
@@ -19308,10 +19317,10 @@
         <v>259.8</v>
       </c>
       <c r="AZ48" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="BA48" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="BB48">
         <v>76.40000000000001</v>
@@ -19398,7 +19407,7 @@
         <v>1.1799</v>
       </c>
       <c r="CD48" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE48">
         <v>1017</v>
@@ -19446,13 +19455,13 @@
         <v>0</v>
       </c>
       <c r="CT48" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU48">
         <v>8.5</v>
       </c>
       <c r="CV48" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW48">
         <v>74</v>
@@ -19481,22 +19490,22 @@
         <v>134</v>
       </c>
       <c r="E49" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F49" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G49" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="H49" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I49" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J49">
-        <v>112.4</v>
+        <v>113</v>
       </c>
       <c r="K49">
         <v>21.7</v>
@@ -19526,13 +19535,13 @@
         <v>0</v>
       </c>
       <c r="T49" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U49" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="V49" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="W49">
         <v>0.6667</v>
@@ -19622,10 +19631,10 @@
         <v>262.7</v>
       </c>
       <c r="AZ49" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="BA49" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="BB49">
         <v>67.2</v>
@@ -19712,7 +19721,7 @@
         <v>1.1836</v>
       </c>
       <c r="CD49" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE49">
         <v>907</v>
@@ -19760,13 +19769,13 @@
         <v>0</v>
       </c>
       <c r="CT49" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU49">
         <v>8.699999999999999</v>
       </c>
       <c r="CV49" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW49">
         <v>72</v>
@@ -19795,22 +19804,22 @@
         <v>135</v>
       </c>
       <c r="E50" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F50" t="s">
         <v>120</v>
       </c>
       <c r="G50" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="H50" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I50" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="J50">
-        <v>112.3</v>
+        <v>112.8</v>
       </c>
       <c r="K50">
         <v>19.2</v>
@@ -19840,13 +19849,13 @@
         <v>0</v>
       </c>
       <c r="T50" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U50" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="V50" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="W50">
         <v>0.1667</v>
@@ -19936,10 +19945,10 @@
         <v>232.2</v>
       </c>
       <c r="AZ50" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="BA50" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="BB50">
         <v>89.09999999999999</v>
@@ -20026,7 +20035,7 @@
         <v>1.1292</v>
       </c>
       <c r="CD50" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE50">
         <v>2629</v>
@@ -20074,13 +20083,13 @@
         <v>0.1</v>
       </c>
       <c r="CT50" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU50">
         <v>18.4</v>
       </c>
       <c r="CV50" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="CW50">
         <v>89</v>
@@ -20109,22 +20118,22 @@
         <v>135</v>
       </c>
       <c r="E51" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F51" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G51" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="H51" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I51" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="J51">
-        <v>112.3</v>
+        <v>112.8</v>
       </c>
       <c r="K51">
         <v>20.2</v>
@@ -20154,13 +20163,13 @@
         <v>0</v>
       </c>
       <c r="T51" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U51" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="V51" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="W51">
         <v>0.1667</v>
@@ -20250,10 +20259,10 @@
         <v>232.8</v>
       </c>
       <c r="AZ51" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="BA51" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="BB51">
         <v>82.09999999999999</v>
@@ -20340,7 +20349,7 @@
         <v>1.1374</v>
       </c>
       <c r="CD51" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE51">
         <v>2359</v>
@@ -20388,13 +20397,13 @@
         <v>0</v>
       </c>
       <c r="CT51" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU51">
         <v>21.1</v>
       </c>
       <c r="CV51" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="CW51">
         <v>85</v>
@@ -20423,22 +20432,22 @@
         <v>135</v>
       </c>
       <c r="E52" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F52" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G52" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="H52" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I52" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="J52">
-        <v>112.3</v>
+        <v>112.8</v>
       </c>
       <c r="K52">
         <v>21.2</v>
@@ -20468,13 +20477,13 @@
         <v>0</v>
       </c>
       <c r="T52" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U52" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="V52" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="W52">
         <v>0.1667</v>
@@ -20564,10 +20573,10 @@
         <v>218.9</v>
       </c>
       <c r="AZ52" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="BA52" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="BB52">
         <v>61.4</v>
@@ -20654,7 +20663,7 @@
         <v>1.1454</v>
       </c>
       <c r="CD52" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE52">
         <v>2090</v>
@@ -20702,13 +20711,13 @@
         <v>0</v>
       </c>
       <c r="CT52" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU52">
         <v>13.6</v>
       </c>
       <c r="CV52" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW52">
         <v>81</v>
@@ -20737,22 +20746,22 @@
         <v>135</v>
       </c>
       <c r="E53" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F53" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="G53" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="H53" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I53" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="J53">
-        <v>112.3</v>
+        <v>112.8</v>
       </c>
       <c r="K53">
         <v>22.2</v>
@@ -20782,13 +20791,13 @@
         <v>18.8</v>
       </c>
       <c r="T53" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U53" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="V53" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="W53">
         <v>0.1667</v>
@@ -20878,10 +20887,10 @@
         <v>216</v>
       </c>
       <c r="AZ53" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BA53" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BB53">
         <v>52.7</v>
@@ -20968,7 +20977,7 @@
         <v>1.1502</v>
       </c>
       <c r="CD53" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE53">
         <v>1940</v>
@@ -21016,13 +21025,13 @@
         <v>0</v>
       </c>
       <c r="CT53" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU53">
         <v>20.7</v>
       </c>
       <c r="CV53" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="CW53">
         <v>80</v>
@@ -21051,22 +21060,22 @@
         <v>136</v>
       </c>
       <c r="E54" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F54" t="s">
         <v>121</v>
       </c>
       <c r="G54" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H54" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I54" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J54">
-        <v>112.4</v>
+        <v>113</v>
       </c>
       <c r="K54">
         <v>19.6</v>
@@ -21096,13 +21105,13 @@
         <v>0</v>
       </c>
       <c r="T54" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U54" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="V54" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="W54">
         <v>0.6333</v>
@@ -21192,10 +21201,10 @@
         <v>223.3</v>
       </c>
       <c r="AZ54" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BA54" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BB54">
         <v>91</v>
@@ -21282,7 +21291,7 @@
         <v>1.1591</v>
       </c>
       <c r="CD54" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE54">
         <v>1658</v>
@@ -21330,13 +21339,13 @@
         <v>0.2</v>
       </c>
       <c r="CT54" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU54">
         <v>9.6</v>
       </c>
       <c r="CV54" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW54">
         <v>83</v>
@@ -21365,22 +21374,22 @@
         <v>136</v>
       </c>
       <c r="E55" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F55" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G55" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H55" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I55" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J55">
-        <v>112.4</v>
+        <v>113</v>
       </c>
       <c r="K55">
         <v>20.6</v>
@@ -21410,13 +21419,13 @@
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U55" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="V55" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="W55">
         <v>0.6333</v>
@@ -21506,10 +21515,10 @@
         <v>217.9</v>
       </c>
       <c r="AZ55" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BA55" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BB55">
         <v>88.59999999999999</v>
@@ -21596,7 +21605,7 @@
         <v>1.1657</v>
       </c>
       <c r="CD55" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE55">
         <v>1457</v>
@@ -21644,13 +21653,13 @@
         <v>0.2</v>
       </c>
       <c r="CT55" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU55">
         <v>8.9</v>
       </c>
       <c r="CV55" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW55">
         <v>80</v>
@@ -21679,22 +21688,22 @@
         <v>136</v>
       </c>
       <c r="E56" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F56" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G56" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H56" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I56" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J56">
-        <v>112.4</v>
+        <v>113</v>
       </c>
       <c r="K56">
         <v>21.6</v>
@@ -21724,13 +21733,13 @@
         <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U56" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="V56" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="W56">
         <v>0.6333</v>
@@ -21814,16 +21823,16 @@
         <v>3.7</v>
       </c>
       <c r="AX56" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AY56">
         <v>199.6</v>
       </c>
       <c r="AZ56" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BA56" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BB56">
         <v>87.3</v>
@@ -21910,7 +21919,7 @@
         <v>1.1724</v>
       </c>
       <c r="CD56" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE56">
         <v>1252</v>
@@ -21958,13 +21967,13 @@
         <v>0.1</v>
       </c>
       <c r="CT56" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU56">
         <v>9.300000000000001</v>
       </c>
       <c r="CV56" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW56">
         <v>77</v>
@@ -21993,22 +22002,22 @@
         <v>136</v>
       </c>
       <c r="E57" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F57" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G57" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H57" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I57" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J57">
-        <v>112.4</v>
+        <v>113</v>
       </c>
       <c r="K57">
         <v>22.6</v>
@@ -22038,13 +22047,13 @@
         <v>0</v>
       </c>
       <c r="T57" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U57" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="V57" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="W57">
         <v>0.6333</v>
@@ -22128,16 +22137,16 @@
         <v>2.9</v>
       </c>
       <c r="AX57" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AY57">
         <v>195.7</v>
       </c>
       <c r="AZ57" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BA57" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BB57">
         <v>78.90000000000001</v>
@@ -22224,7 +22233,7 @@
         <v>1.1772</v>
       </c>
       <c r="CD57" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="CE57">
         <v>1107</v>
@@ -22272,13 +22281,13 @@
         <v>0</v>
       </c>
       <c r="CT57" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU57">
         <v>11.1</v>
       </c>
       <c r="CV57" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW57">
         <v>75</v>
@@ -22307,22 +22316,22 @@
         <v>137</v>
       </c>
       <c r="E58" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F58" t="s">
         <v>122</v>
       </c>
       <c r="G58" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="H58" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I58" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="J58">
-        <v>538.3</v>
+        <v>538.8</v>
       </c>
       <c r="K58">
         <v>19.7</v>
@@ -22352,13 +22361,13 @@
         <v>0</v>
       </c>
       <c r="T58" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U58" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="V58" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="W58">
         <v>0.6667</v>
@@ -22448,10 +22457,10 @@
         <v>223.2</v>
       </c>
       <c r="AZ58" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BA58" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="BB58">
         <v>92.09999999999999</v>
@@ -22538,7 +22547,7 @@
         <v>1.1231</v>
       </c>
       <c r="CD58" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE58">
         <v>2905</v>
@@ -22586,13 +22595,13 @@
         <v>0</v>
       </c>
       <c r="CT58" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU58">
         <v>8.800000000000001</v>
       </c>
       <c r="CV58" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW58">
         <v>99</v>
@@ -22621,22 +22630,22 @@
         <v>137</v>
       </c>
       <c r="E59" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F59" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G59" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="H59" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I59" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="J59">
-        <v>538.3</v>
+        <v>538.8</v>
       </c>
       <c r="K59">
         <v>20.7</v>
@@ -22666,13 +22675,13 @@
         <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U59" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="V59" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="W59">
         <v>0.6667</v>
@@ -22756,16 +22765,16 @@
         <v>10.9</v>
       </c>
       <c r="AX59" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AY59">
         <v>211.9</v>
       </c>
       <c r="AZ59" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BA59" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BB59">
         <v>94.09999999999999</v>
@@ -22852,7 +22861,7 @@
         <v>1.1333</v>
       </c>
       <c r="CD59" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE59">
         <v>2564</v>
@@ -22900,13 +22909,13 @@
         <v>0</v>
       </c>
       <c r="CT59" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU59">
         <v>6.2</v>
       </c>
       <c r="CV59" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW59">
         <v>94</v>
@@ -22935,22 +22944,22 @@
         <v>137</v>
       </c>
       <c r="E60" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F60" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G60" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="H60" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I60" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="J60">
-        <v>538.3</v>
+        <v>538.8</v>
       </c>
       <c r="K60">
         <v>21.7</v>
@@ -22980,13 +22989,13 @@
         <v>0</v>
       </c>
       <c r="T60" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U60" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="V60" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="W60">
         <v>0.6667</v>
@@ -23070,16 +23079,16 @@
         <v>10.1</v>
       </c>
       <c r="AX60" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AY60">
         <v>207.5</v>
       </c>
       <c r="AZ60" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BA60" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BB60">
         <v>94.40000000000001</v>
@@ -23166,7 +23175,7 @@
         <v>1.147</v>
       </c>
       <c r="CD60" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE60">
         <v>2127</v>
@@ -23214,13 +23223,13 @@
         <v>0</v>
       </c>
       <c r="CT60" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU60">
         <v>6.1</v>
       </c>
       <c r="CV60" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW60">
         <v>86</v>
@@ -23249,22 +23258,22 @@
         <v>137</v>
       </c>
       <c r="E61" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F61" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="G61" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="H61" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I61" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="J61">
-        <v>538.3</v>
+        <v>538.8</v>
       </c>
       <c r="K61">
         <v>22.7</v>
@@ -23294,13 +23303,13 @@
         <v>0</v>
       </c>
       <c r="T61" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U61" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="V61" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="W61">
         <v>0.6667</v>
@@ -23384,16 +23393,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AX61" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AY61">
         <v>204.9</v>
       </c>
       <c r="AZ61" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BA61" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="BB61">
         <v>93</v>
@@ -23480,7 +23489,7 @@
         <v>1.1571</v>
       </c>
       <c r="CD61" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CE61">
         <v>1813</v>
@@ -23528,13 +23537,13 @@
         <v>0</v>
       </c>
       <c r="CT61" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CU61">
         <v>6.5</v>
       </c>
       <c r="CV61" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="CW61">
         <v>81</v>
@@ -23681,7 +23690,7 @@
         <v>138</v>
       </c>
       <c r="P2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q2">
         <v>5</v>
@@ -23734,7 +23743,7 @@
         <v>138</v>
       </c>
       <c r="P3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -23787,7 +23796,7 @@
         <v>138</v>
       </c>
       <c r="P4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q4">
         <v>5</v>
@@ -23840,7 +23849,7 @@
         <v>138</v>
       </c>
       <c r="P5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q5">
         <v>5</v>
@@ -23893,7 +23902,7 @@
         <v>138</v>
       </c>
       <c r="P6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q6">
         <v>5</v>
@@ -23946,7 +23955,7 @@
         <v>138</v>
       </c>
       <c r="P7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -23999,7 +24008,7 @@
         <v>138</v>
       </c>
       <c r="P8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q8">
         <v>5</v>
@@ -24052,7 +24061,7 @@
         <v>138</v>
       </c>
       <c r="P9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -24105,7 +24114,7 @@
         <v>138</v>
       </c>
       <c r="P10" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -24158,7 +24167,7 @@
         <v>138</v>
       </c>
       <c r="P11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -24211,7 +24220,7 @@
         <v>138</v>
       </c>
       <c r="P12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q12">
         <v>5</v>
@@ -24264,7 +24273,7 @@
         <v>138</v>
       </c>
       <c r="P13" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q13">
         <v>5</v>
@@ -24317,7 +24326,7 @@
         <v>139</v>
       </c>
       <c r="P14" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q14">
         <v>5</v>
@@ -24370,7 +24379,7 @@
         <v>140</v>
       </c>
       <c r="P15" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -24423,7 +24432,7 @@
         <v>138</v>
       </c>
       <c r="P16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q16">
         <v>5</v>
